--- a/server/excel/release/collection.xlsx
+++ b/server/excel/release/collection.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="藏品穿戴要求" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="藏品基础" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="藏品随机属性组" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="藏品礼包" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="功能配置" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="藏品随机英雄组" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="专属种族属性组包" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="专属职业属性组包" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="专属英雄属性组包" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="固定属性藏品" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="专属英雄技能" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Sheet1" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="藏品回收" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="藏品召唤方式" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="藏品召唤阶段奖励" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="藏品召唤作弊" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="藏品召唤奖池组" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="藏品召唤对话气泡" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="属性升级组" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="藏品推荐" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Sheet2" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="藏品穿戴要求" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="藏品基础" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="藏品随机属性组" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="藏品礼包" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能配置" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="藏品随机英雄组" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="专属种族属性组包" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="专属职业属性组包" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="专属英雄属性组包" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定属性藏品" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="专属英雄技能" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="藏品回收" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="藏品召唤方式" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="藏品召唤阶段奖励" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="藏品召唤作弊" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="藏品召唤奖池组" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="藏品召唤对话气泡" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性升级组" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="藏品推荐" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1003,7 +1003,7 @@
     <t xml:space="preserve">10002:21</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhân tộc: &lt;2408 Na Tra &gt;; Tiên Tộc: &lt;2408 Huyền Trang &gt;; Yêu tộc: &lt;2408 Ngưu Ma Vương &gt;; Ma tộc: &lt;2408 Hình Thiên &gt;, &lt;2408 Hoàng Tuyền &gt;, &lt;2408 Chúc Long &gt;</t>
+    <t xml:space="preserve">Tân Binh: &lt;2408 S.Sanji&gt;; Hải Tặc: &lt;2408 Perospero&gt;; Dũng Sĩ: &lt;2408 Gan Fall&gt;; Ngũ Hoàng: &lt;2408 Mihawk&gt;, &lt;2408 Jinbe&gt;, &lt;2408 Marco&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Huyết U Châu</t>
@@ -1054,7 +1054,7 @@
     <t xml:space="preserve">10000:207</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhân tộc: &lt;2408 Cơ Phát &gt;; Tiên Tộc: &lt;2408 Đấu Chiến Thắng Phật &gt;; Yêu tộc: &lt;2408 Ngao Bính &gt;</t>
+    <t xml:space="preserve">Tân Binh: &lt;2408 Franky&gt;; Hải Tặc: &lt;2408 Ace&gt;; Dũng Sĩ: &lt;2408 Judge&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">10000:197</t>
@@ -1069,7 +1069,7 @@
     <t xml:space="preserve">Cân đối</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhân tộc: &lt;2408 Hậu Nghệ &gt;, &lt;2408 Hoa Mộc Lan &gt;; Yêu tộc: &lt;2408 Hỗn Thiên Đại Thánh &gt;, &lt;2408 Giơ cao thương &gt;, &lt;2408 Kim Ô &gt;; Thần tộc: &lt;2408 Ngọc Đế &gt;; Ma tộc: &lt;2408 Ma · Ngộ Không &gt;; Hỗn độn tộc: &lt;2408 Ảnh &gt;</t>
+    <t xml:space="preserve">Tân Binh: &lt;2408 S.Usopp&gt;; Dũng Sĩ: &lt;2408 Ichiji&gt;, &lt;2408 Niji&gt;, &lt;2408 ryuma&gt;; Hải Quân: &lt;2408 Lucci&gt;; Ngũ Hoàng: &lt;2408 Luffy Gear 3&gt;; Siêu cấp: &lt;2408 S.Rozo&gt;, &lt;2408 Luffy Gear4&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">14:258</t>
@@ -1102,7 +1102,7 @@
     <t xml:space="preserve">2004:432</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhân tộc: &lt;2408 Lôi Chấn Tử &gt;; Tiên Tộc: &lt;2408 Vân Trung Tử &gt;; Yêu tộc: &lt;2408 Khổng Tuyên &gt;; Thần tộc: &lt;2408 Cộng Công &gt;; Ma tộc: &lt;2408 Minh Hà &gt;</t>
+    <t xml:space="preserve">Hải Tặc: &lt;2408 Burgess&gt;; Dũng Sĩ: &lt;2408 Reiju&gt;; Hải Quân: &lt;2408 Kizazu&gt;; Ngũ Hoàng: &lt;2408 Sabo&gt;; Siêu cấp: &lt;2408 Law&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">10004:16</t>
@@ -1117,13 +1117,13 @@
     <t xml:space="preserve">10004:20</t>
   </si>
   <si>
-    <t xml:space="preserve">Yêu tộc: &lt;2408 Bạch Cốt phu nhân &gt;; Thần tộc: &lt;2408 Cửu Thiên Huyền Nữ &gt;; Ma tộc: &lt;2408 Đông Hoàng Thái Nhất &gt;, &lt;2408 Linh môi ma nữ &gt;</t>
+    <t xml:space="preserve">Dũng Sĩ: &lt;2408 Hogback&gt;; Hải Quân: &lt;2408 Magellan&gt;; Ngũ Hoàng: &lt;2408 King&gt;, &lt;2408 Big Mom&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">5:246</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhân tộc: &lt;2408 Khương Tử Nha &gt;; Tiên Tộc: &lt;2408 Thông Thiên giáo chủ &gt;, &lt;2408 Nguyên Thủy Thiên Tôn &gt;; Yêu tộc: &lt;2408 Ðát Kỷ &gt;; Thần tộc: &lt;2408 Chúc Dung &gt;; Ma tộc: &lt;2408 Diêm Quân &gt;</t>
+    <t xml:space="preserve">Tân Binh: &lt;2408 Robin&gt;; Hải Tặc: &lt;2408 Cracker&gt;, &lt;2408 Bellamy&gt;; Dũng Sĩ: &lt;2408 Enel&gt;; Hải Quân: &lt;2408 Aokiji&gt;; Ngũ Hoàng: &lt;2408 Doflamingo&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Phòng ngự</t>
@@ -1138,7 +1138,7 @@
     <t xml:space="preserve">10001:4</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhân tộc: &lt;2408 Lý Tĩnh &gt;; Yêu tộc: &lt;2408 Hồng hài nhi &gt;; Thần tộc: &lt;2408 Dương Tiễn &gt;</t>
+    <t xml:space="preserve">Tân Binh: &lt;2408 Brook&gt;; Dũng Sĩ: &lt;2408 Zephyr&gt;; Hải Quân: &lt;2408 Vergo&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">17:270</t>
@@ -1165,25 +1165,25 @@
     <t xml:space="preserve">6:270</t>
   </si>
   <si>
-    <t xml:space="preserve">Tiên Tộc: &lt;2408 Quyển Liêm Đại Tướng &gt;</t>
+    <t xml:space="preserve">Hải Tặc: &lt;2408 Katakuri&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Tiên Tộc: &lt;2408 Thiên Bồng nguyên soái &gt;; Thần tộc: &lt;2408 Bàn Cổ &gt;; Ma tộc: &lt;2408 Xi Vưu &gt;</t>
+    <t xml:space="preserve">Hải Tặc: &lt;2408 Krieg&gt;; Hải Quân: &lt;2408 Garp&gt;; Ngũ Hoàng: &lt;2408 Ivankov&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Trị liệu</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhân tộc: &lt;2408 Hằng Nga &gt;; Tiên Tộc: &lt;2408 Nam Cực tiên tử &gt;; Thần tộc: &lt;2408 Côn &gt;; Ma tộc: &lt;2408 Dạ Mị &gt;</t>
+    <t xml:space="preserve">Tân Binh: &lt;2408 S.Nami&gt;; Hải Tặc: &lt;2408 Marguerite&gt;; Hải Quân: &lt;2408 Tashigi&gt;; Ngũ Hoàng: &lt;2408 Inazuma&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Trạng thái phụ trợ</t>
   </si>
   <si>
-    <t xml:space="preserve">Yêu tộc: &lt;2408 Thạch Cơ &gt;; Thần tộc: &lt;2408 Nữ Oa &gt;; Ma tộc: &lt;2408 Mạnh bà &gt;</t>
+    <t xml:space="preserve">Dũng Sĩ: &lt;2408 Shura&gt;; Hải Quân: &lt;2408 Kalifa&gt;; Ngũ Hoàng: &lt;2408 Hancook&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhân tộc: &lt;2408 Đặng Ngọc thiền &gt;; Tiên Tộc: &lt;2408 Lộc duyên thượng tiên &gt;; Thần tộc: &lt;2408 Thần Nông &gt;</t>
+    <t xml:space="preserve">Tân Binh: &lt;2408 Hawkins&gt;; Hải Tặc: &lt;2408 Perona&gt;; Hải Quân: &lt;2408 Smoker&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">斗山神佛</t>
